--- a/artfynd/A 32755-2020 artfynd.xlsx
+++ b/artfynd/A 32755-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32755-2020 artfynd.xlsx
+++ b/artfynd/A 32755-2020 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>127163902</v>
       </c>
       <c r="B3" t="n">
-        <v>95985</v>
+        <v>96060</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>127163903</v>
       </c>
       <c r="B4" t="n">
-        <v>95985</v>
+        <v>96060</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>127163904</v>
       </c>
       <c r="B5" t="n">
-        <v>95985</v>
+        <v>96060</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
